--- a/docs/downloads/04/tbl_other_act_all_marovoay_bepako.xlsx
+++ b/docs/downloads/04/tbl_other_act_all_marovoay_bepako.xlsx
@@ -387,12 +387,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Animateur rural, alphabétiseur ? Mpanentana eny ambanivohitra, Mpampianatra mamaky teny sy manoratra</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +411,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -477,12 +459,6 @@
           <t>Démarcheur et Kinanga autre que produit de pêche - Mpanelanelana sy kinanga amin?ny vokatra hafa ankoatra ny jono</t>
         </is>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -513,12 +489,6 @@
           <t>Employé permanent d?un ménage et membre de ce ménage ? Mpiasa raikitra ao @ tokantrano iray sady mipetraka ao aminy</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +501,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,12 +513,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,12 +525,6 @@
           <t>Gargotier - Mpivarotra hani-masaka</t>
         </is>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -621,12 +573,6 @@
           <t>Porteur d'eau - Mpaka rano</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +585,6 @@
           <t>Pêcheur exploitant- Mpanjono miasa tena</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -657,12 +597,6 @@
           <t>Retraité - Misotro ronono, mandray fisotroan-dronono</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -688,12 +622,6 @@
           <t>Activités domestiques - Asa an-trano</t>
         </is>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +634,6 @@
           <t>Aide Sanitaire</t>
         </is>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +646,6 @@
           <t>Animateur rural, alphabétiseur ? Mpanentana eny ambanivohitra, Mpampianatra mamaky teny sy manoratra</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,12 +658,6 @@
           <t>Artisan NCA (exerçant un métier manuel à son propre compte) - Mpanao asa tanana tsy voasokajy teo aloha miasa tena</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +670,6 @@
           <t>Autres activités libérales - Asa mahaleo-tena hafa</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -778,12 +682,6 @@
           <t>Barman, serveur - Mpiasa @ trano fisotroana, mpandroso sakafo</t>
         </is>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -796,12 +694,6 @@
           <t>Collecteur (riz) - Mpanangom-bary</t>
         </is>
       </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -832,12 +724,6 @@
           <t>Conducteur de véhicule, engin, transporteur camion et voiture - Mpamily fiara, Mpitatitra @ fiara, fiarabe?</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -850,12 +736,6 @@
           <t>Couturier, tailleur - Mpanjaitra</t>
         </is>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -886,12 +766,6 @@
           <t>Docker, manutentionnaire, porteur - Mpibata entana, Mpanao kibaroa</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -904,12 +778,6 @@
           <t>Démarcheur de bétail-Mpanao dabokandro</t>
         </is>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -922,12 +790,6 @@
           <t>Démarcheur et Kinanga autre que produit de pêche - Mpanelanelana sy kinanga amin?ny vokatra hafa ankoatra ny jono</t>
         </is>
       </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-      <c r="D32">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -976,12 +838,6 @@
           <t>Employé du secteur tertiaire (commerce, administration, service) : gérant, agent, secrétaire, caissier, vendeur, comptable, aide-comptable,... - Mpiasa amin?ny fandraharahana momba ny varotra, mpitantsoratra, mpandray vola, mpitantambola na ny mpanampy az</t>
         </is>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1012,12 +868,6 @@
           <t>Enseignant du primaire - Mpampianatra @ fanabeazana fototra</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1030,12 +880,6 @@
           <t>Enseignant du secondaire - Mpampianatra @ Ambaratonga faharoa</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1048,12 +892,6 @@
           <t>Exploitant minier, prospecteur de pierres et métaux précieux (rubis, saphir, or...) - Mpitrandraka vato, na vy sarobidy</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1066,12 +904,6 @@
           <t>Exploitantforestier, bûcheron, charbonnier- Mpitrandraka ala, mpamaky kitay, mpanao arina</t>
         </is>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1084,12 +916,6 @@
           <t>Fournisseur de matières premières pour les matériaux de construction - Mpamatsy akora @ fanamboarana trano -</t>
         </is>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1102,12 +928,6 @@
           <t>Gardien de bétail (Salarié) - Mpikarama miandry omby</t>
         </is>
       </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="D42">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1156,12 +976,6 @@
           <t>Machiniste, ajusteur, tourneur, fraiseur, rectificateur, soudeur, mécanicien - Mpanao asa momba ny vy</t>
         </is>
       </c>
-      <c r="C45">
-        <v>2</v>
-      </c>
-      <c r="D45">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1174,12 +988,6 @@
           <t>Man?uvre ou ouvrier (entreprise et société) - ) - Mpanampy @ taotrano</t>
         </is>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1192,12 +1000,6 @@
           <t>Maçon, Ouvrier du bâtiment, peintre en bâtiment, Plombier - Mpandalotra, Mpiasa @ taotrano, Mpiasa mikarakara ny rano</t>
         </is>
       </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-      <c r="D47">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1210,12 +1012,6 @@
           <t>Membre d?un ménage mais employé permanent chez un autre ménage ? Olona mpikambana ao @ tokantrano iray fa mpiasa raikitra any @ tokantrano hafa</t>
         </is>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1228,12 +1024,6 @@
           <t>Menuisier, charpentier, Ebéniste, Sculpteur - Mpandrafitra hazo, trano, Mpanao sary sokitra</t>
         </is>
       </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1246,12 +1036,6 @@
           <t>Mécanicien- Mpanamboatra fiarakodia</t>
         </is>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1282,12 +1066,6 @@
           <t>Ouvrier d'entretien, bricoleur (kibaroa) - Kibaroa, manao izay asa hita</t>
         </is>
       </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1300,12 +1078,6 @@
           <t>Piroguier - Mpivoy lakana</t>
         </is>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1318,12 +1090,6 @@
           <t>Porteur d'eau - Mpaka rano</t>
         </is>
       </c>
-      <c r="C54">
-        <v>2</v>
-      </c>
-      <c r="D54">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1336,12 +1102,6 @@
           <t>Producteur de toaka gasy, de betsa - Mpamboatra toaka gasy, betsa</t>
         </is>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1372,12 +1132,6 @@
           <t>Retraité - Misotro ronono, mandray fisotroan-dronono</t>
         </is>
       </c>
-      <c r="C57">
-        <v>2</v>
-      </c>
-      <c r="D57">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1389,12 +1143,6 @@
         <is>
           <t>Sage-femme, infirmier - Mpampivelona, mpitsabo mpanampy</t>
         </is>
-      </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58">
-        <v>0.1</v>
       </c>
     </row>
     <row r="59">
